--- a/data/dividends_info_20260623.xlsx
+++ b/data/dividends_info_20260623.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>64.12999725341797</v>
+        <v>63.47000122070312</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1403399405185585</v>
+        <v>0.1417992725209577</v>
       </c>
       <c r="J2" t="n">
         <v>265</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65.84999847412109</v>
+        <v>65.55000305175781</v>
       </c>
       <c r="I3" t="n">
-        <v>1.063022044374228</v>
+        <v>1.067887059360295</v>
       </c>
       <c r="J3" t="n">
         <v>244</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.239999771118164</v>
+        <v>9.220000267028809</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6493506654355597</v>
+        <v>0.6507592002417079</v>
       </c>
       <c r="J4" t="n">
         <v>174</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>64.12999725341797</v>
+        <v>63.47000122070312</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1403399405185585</v>
+        <v>0.1417992725209577</v>
       </c>
       <c r="J6" t="n">
         <v>174</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.035000085830688</v>
+        <v>2.025000095367432</v>
       </c>
       <c r="I7" t="n">
-        <v>3.783783624194224</v>
+        <v>3.802468956725087</v>
       </c>
       <c r="J7" t="n">
         <v>153</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>21.59000015258789</v>
+        <v>21.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.250578962907679</v>
+        <v>1.255813953488372</v>
       </c>
       <c r="J8" t="n">
         <v>153</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.900000095367432</v>
+        <v>5.940000057220459</v>
       </c>
       <c r="I9" t="n">
-        <v>3.389830453681454</v>
+        <v>3.367003334568775</v>
       </c>
       <c r="J9" t="n">
         <v>146</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.25</v>
+        <v>7.400000095367432</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.8108108003614941</v>
       </c>
       <c r="J10" t="n">
         <v>118</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.59000015258789</v>
+        <v>21.5</v>
       </c>
       <c r="I14" t="n">
-        <v>1.250578962907679</v>
+        <v>1.255813953488372</v>
       </c>
       <c r="J14" t="n">
         <v>90</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>64.12999725341797</v>
+        <v>63.47000122070312</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1403399405185585</v>
+        <v>0.1417992725209577</v>
       </c>
       <c r="J15" t="n">
         <v>90</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.960000038146973</v>
+        <v>6.039999961853027</v>
       </c>
       <c r="I16" t="n">
-        <v>5.03355701476259</v>
+        <v>4.966887448588033</v>
       </c>
       <c r="J16" t="n">
         <v>83</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.599999904632568</v>
+        <v>5.619999885559082</v>
       </c>
       <c r="I19" t="n">
-        <v>4.464285790312048</v>
+        <v>4.448398667095876</v>
       </c>
       <c r="J19" t="n">
         <v>34</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.21999979019165</v>
+        <v>4.210000038146973</v>
       </c>
       <c r="I20" t="n">
-        <v>3.317535709963671</v>
+        <v>3.325415646827901</v>
       </c>
       <c r="J20" t="n">
         <v>27</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9.859999656677246</v>
+        <v>9.899999618530273</v>
       </c>
       <c r="I21" t="n">
-        <v>2.63691692751659</v>
+        <v>2.626262727458558</v>
       </c>
       <c r="J21" t="n">
         <v>27</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>15.35999965667725</v>
+        <v>15.14000034332275</v>
       </c>
       <c r="I22" t="n">
-        <v>3.906250087311494</v>
+        <v>3.963011799168287</v>
       </c>
       <c r="J22" t="n">
         <v>27</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3.513999938964844</v>
+        <v>3.456000089645386</v>
       </c>
       <c r="I23" t="n">
-        <v>6.260671708059498</v>
+        <v>6.365740575619425</v>
       </c>
       <c r="J23" t="n">
         <v>27</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.360000133514404</v>
+        <v>6.329999923706055</v>
       </c>
       <c r="I25" t="n">
-        <v>1.572327011017562</v>
+        <v>1.579778850004354</v>
       </c>
       <c r="J25" t="n">
         <v>27</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.140000104904175</v>
+        <v>2.180000066757202</v>
       </c>
       <c r="I30" t="n">
-        <v>3.971962422114281</v>
+        <v>3.899082449407415</v>
       </c>
       <c r="J30" t="n">
         <v>13</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.809999942779541</v>
+        <v>4.800000190734863</v>
       </c>
       <c r="I31" t="n">
-        <v>1.455301472613933</v>
+        <v>1.458333275384376</v>
       </c>
       <c r="J31" t="n">
         <v>13</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>35.54999923706055</v>
+        <v>35.95000076293945</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4219409373253273</v>
+        <v>0.4172461663884962</v>
       </c>
       <c r="J32" t="n">
         <v>13</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>21.40999984741211</v>
+        <v>21.42000007629395</v>
       </c>
       <c r="I34" t="n">
-        <v>1.167678663156171</v>
+        <v>1.16713351591759</v>
       </c>
       <c r="J34" t="n">
         <v>-1</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>28.89999961853027</v>
+        <v>29.25</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6747404933354004</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="J35" t="n">
         <v>-1</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.825000047683716</v>
+        <v>1.840000033378601</v>
       </c>
       <c r="I36" t="n">
-        <v>1.808219130836928</v>
+        <v>1.793478228334894</v>
       </c>
       <c r="J36" t="n">
         <v>-1</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.179999828338623</v>
+        <v>5.139999866485596</v>
       </c>
       <c r="I37" t="n">
-        <v>5.59845578398429</v>
+        <v>5.642023492858249</v>
       </c>
       <c r="J37" t="n">
         <v>-1</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.619999885559082</v>
+        <v>3.655999898910522</v>
       </c>
       <c r="I38" t="n">
-        <v>4.419889642490671</v>
+        <v>4.376367735887507</v>
       </c>
       <c r="J38" t="n">
         <v>-1</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.503999948501587</v>
+        <v>2.519999980926514</v>
       </c>
       <c r="I39" t="n">
-        <v>5.53514388380636</v>
+        <v>5.500000041628641</v>
       </c>
       <c r="J39" t="n">
         <v>-1</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>50.38999938964844</v>
+        <v>50.43000030517578</v>
       </c>
       <c r="I40" t="n">
-        <v>1.250248080235977</v>
+        <v>1.249256387443133</v>
       </c>
       <c r="J40" t="n">
         <v>-1</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6.074999809265137</v>
+        <v>6.119999885559082</v>
       </c>
       <c r="I41" t="n">
-        <v>2.304526821325697</v>
+        <v>2.287581742123032</v>
       </c>
       <c r="J41" t="n">
         <v>-1</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>27.95999908447266</v>
+        <v>27.81999969482422</v>
       </c>
       <c r="I43" t="n">
-        <v>3.040057324150773</v>
+        <v>3.055355892610375</v>
       </c>
       <c r="J43" t="n">
         <v>-1</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>64.12999725341797</v>
+        <v>63.47000122070312</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1403399405185585</v>
+        <v>0.1417992725209577</v>
       </c>
       <c r="J44" t="n">
         <v>-1</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.399999976158142</v>
+        <v>1.429999947547913</v>
       </c>
       <c r="I45" t="n">
-        <v>0.7142857264499277</v>
+        <v>0.699300724950897</v>
       </c>
       <c r="J45" t="n">
         <v>-1</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.202000141143799</v>
+        <v>6.190000057220459</v>
       </c>
       <c r="I46" t="n">
-        <v>2.923250497807372</v>
+        <v>2.928917581971889</v>
       </c>
       <c r="J46" t="n">
         <v>-1</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>8.550000190734863</v>
+        <v>8.630000114440918</v>
       </c>
       <c r="I47" t="n">
-        <v>3.040935604676908</v>
+        <v>3.012746194115708</v>
       </c>
       <c r="J47" t="n">
         <v>-1</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>10.09000015258789</v>
+        <v>10.14000034332275</v>
       </c>
       <c r="I48" t="n">
-        <v>2.745292327165672</v>
+        <v>2.731755331570635</v>
       </c>
       <c r="J48" t="n">
         <v>-1</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.019999980926514</v>
+        <v>1.034999966621399</v>
       </c>
       <c r="I49" t="n">
-        <v>1.32352943651404</v>
+        <v>1.304347868151988</v>
       </c>
       <c r="J49" t="n">
         <v>-8</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.022000074386597</v>
+        <v>2.980000019073486</v>
       </c>
       <c r="I50" t="n">
-        <v>3.639973437867229</v>
+        <v>3.691275144159233</v>
       </c>
       <c r="J50" t="n">
         <v>-8</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.994999885559082</v>
+        <v>3.009999990463257</v>
       </c>
       <c r="I52" t="n">
-        <v>5.342237265900012</v>
+        <v>5.315614634781944</v>
       </c>
       <c r="J52" t="n">
         <v>-15</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.8450000286102295</v>
+        <v>0.8650000095367432</v>
       </c>
       <c r="I53" t="n">
-        <v>2.958579781484442</v>
+        <v>2.890173378540068</v>
       </c>
       <c r="J53" t="n">
         <v>-15</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>27.39999961853027</v>
+        <v>27.29999923706055</v>
       </c>
       <c r="I54" t="n">
-        <v>4.051094946911317</v>
+        <v>4.065934179562696</v>
       </c>
       <c r="J54" t="n">
         <v>-19</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.9010000228881836</v>
+        <v>0.8920000195503235</v>
       </c>
       <c r="I55" t="n">
-        <v>3.329633655705586</v>
+        <v>3.363228625838332</v>
       </c>
       <c r="J55" t="n">
         <v>-22</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.4650000035762787</v>
+        <v>0.4699999988079071</v>
       </c>
       <c r="I56" t="n">
-        <v>4.946236521098666</v>
+        <v>4.893617033688609</v>
       </c>
       <c r="J56" t="n">
         <v>-22</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>19.39999961853027</v>
+        <v>19.5</v>
       </c>
       <c r="I57" t="n">
-        <v>3.092783565969242</v>
+        <v>3.076923076923077</v>
       </c>
       <c r="J57" t="n">
         <v>-22</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>9.060000419616699</v>
+        <v>9.039999961853027</v>
       </c>
       <c r="I58" t="n">
-        <v>2.207505416522502</v>
+        <v>2.21238938986681</v>
       </c>
       <c r="J58" t="n">
         <v>-22</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.369999885559082</v>
+        <v>2.394999980926514</v>
       </c>
       <c r="I59" t="n">
-        <v>7.594937075599819</v>
+        <v>7.515657679895529</v>
       </c>
       <c r="J59" t="n">
         <v>-29</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>16.75</v>
+        <v>16.70000076293945</v>
       </c>
       <c r="I61" t="n">
-        <v>1.492537313432836</v>
+        <v>1.497005919633241</v>
       </c>
       <c r="J61" t="n">
         <v>-29</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>4</v>
+        <v>3.960000038146973</v>
       </c>
       <c r="I62" t="n">
-        <v>0.75</v>
+        <v>0.7575757502779744</v>
       </c>
       <c r="J62" t="n">
         <v>-29</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>4.420000076293945</v>
+        <v>4.400000095367432</v>
       </c>
       <c r="I63" t="n">
-        <v>3.393665099792738</v>
+        <v>3.409090835200855</v>
       </c>
       <c r="J63" t="n">
         <v>-29</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>12.55000019073486</v>
+        <v>12.64999961853027</v>
       </c>
       <c r="I64" t="n">
-        <v>4.621513873985353</v>
+        <v>4.584980375417487</v>
       </c>
       <c r="J64" t="n">
         <v>-29</v>
@@ -5306,146 +5306,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ACEA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Gismondi 1754 S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Grifal S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>OPS Retail S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Poste Italiane S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Unicredit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>